--- a/healthcare_surveys/021_remote_patient_monitoring_confidence_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/021_remote_patient_monitoring_confidence_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>patient_confidence_in_the_last_28_days</t>
+          <t>patient_confidence_in_the_last_28_days_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Patient Confidence in the Last 28 Days</t>
+          <t>Patient Confidence In The Last 28 Days 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>patient_confidence_in_the_next_7_days</t>
+          <t>patient_confidence_in_the_next_7_days_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Patient Confidence in the Next 7 Days</t>
+          <t>Patient Confidence In The Next 7 Days 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>patient_confidence_in_the_last_7_days</t>
+          <t>patient_confidence_in_the_last_7_days_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Patient Confidence in the Last 7 Days</t>
+          <t>Patient Confidence In The Last 7 Days 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>patient_confidence_in_the_last_28_days</t>
+          <t>patient_confidence_in_the_last_28_days_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Patient Confidence in the Last 28 Days</t>
+          <t>Patient Confidence In The Last 28 Days 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>patient_confidence_in_the_next_28_days</t>
+          <t>patient_confidence_in_the_next_28_days_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patient Confidence in the Next 28 Days</t>
+          <t>Patient Confidence In The Next 28 Days 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1228,7 +1228,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>patient_confidence_in_the_last_28_days_choices</t>
+          <t>patient_confidence_in_the_last_28_days_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>patient_confidence_in_the_last_28_days_choices</t>
+          <t>patient_confidence_in_the_last_28_days_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>patient_confidence_in_the_next_7_days_choices</t>
+          <t>patient_confidence_in_the_next_7_days_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>patient_confidence_in_the_next_7_days_choices</t>
+          <t>patient_confidence_in_the_next_7_days_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>patient_confidence_in_the_last_7_days_choices</t>
+          <t>patient_confidence_in_the_last_7_days_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>patient_confidence_in_the_last_7_days_choices</t>
+          <t>patient_confidence_in_the_last_7_days_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>patient_confidence_in_the_last_28_days_choices</t>
+          <t>patient_confidence_in_the_last_28_days_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>patient_confidence_in_the_last_28_days_choices</t>
+          <t>patient_confidence_in_the_last_28_days_3_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>patient_confidence_in_the_next_28_days_choices</t>
+          <t>patient_confidence_in_the_next_28_days_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>patient_confidence_in_the_next_28_days_choices</t>
+          <t>patient_confidence_in_the_next_28_days_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
